--- a/docs/v2/04_SDT_V2_Production_UAT_Pack.xlsx
+++ b/docs/v2/04_SDT_V2_Production_UAT_Pack.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="UAT Summary" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="301">
   <si>
     <t xml:space="preserve">SDT V2 - Production User Acceptance Testing (UAT) Pack</t>
   </si>
@@ -130,13 +130,13 @@
     <t xml:space="preserve">Critical</t>
   </si>
   <si>
-    <t xml:space="preserve">In UAT</t>
+    <t xml:space="preserve">UAT Done</t>
   </si>
   <si>
     <t xml:space="preserve">TC-001 to TC-004, TC-012 to TC-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending</t>
+    <t xml:space="preserve">Approved</t>
   </si>
   <si>
     <t xml:space="preserve">Production deployment completed; authentication and RLS isolation require formal UAT evidence.</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">TC-021 to TC-024</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary mobile target: 393 × 852 CSS px portrait; desktop regression included.</t>
+    <t xml:space="preserve">Primary mobile target: iPhone16 (393 × 852 CSS px) portrait; desktop regression included.</t>
   </si>
   <si>
     <t xml:space="preserve">CR-003</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">100%</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Assessed</t>
+    <t xml:space="preserve">Passed</t>
   </si>
   <si>
     <t xml:space="preserve">No unresolved critical defects.</t>
@@ -217,9 +217,6 @@
     <t xml:space="preserve">Core V1 regression</t>
   </si>
   <si>
-    <t xml:space="preserve">Passed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Challenge tracking, strikes and reports remain functional.</t>
   </si>
   <si>
@@ -284,9 +281,6 @@
   </si>
   <si>
     <t xml:space="preserve">Actual Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence Ref</t>
   </si>
   <si>
     <t xml:space="preserve">Defect ID</t>
@@ -318,6 +312,43 @@
     <t xml:space="preserve">Blank page, 404/500 error, configuration error, or application fails to render.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">App/website loads properly @ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://self-development-tracker-sdt.vercel.app/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+Authentication screen correctly appears.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-002</t>
   </si>
   <si>
@@ -330,7 +361,7 @@
     <t xml:space="preserve">Dedicated UAT User 1 exists in Supabase</t>
   </si>
   <si>
-    <t xml:space="preserve">Email: uat.sdt.user1@example.com
+    <t xml:space="preserve">Email: sdt.user1@example.com
 Password: use dedicated UAT password</t>
   </si>
   <si>
@@ -347,6 +378,9 @@
     <t xml:space="preserve">Friendly invalid-login message is acceptable only for incorrect credentials. With valid credentials, login failure, unexpected logout after refresh, or another user's data appearing is a defect.</t>
   </si>
   <si>
+    <t xml:space="preserve">Takes 4-5s to load, however login succeeds</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-003</t>
   </si>
   <si>
@@ -369,6 +403,9 @@
   </si>
   <si>
     <t xml:space="preserve">Application crash, indefinite loading, raw server error, or protected data being displayed is a failure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentication is rejected and a clear user-facing error is displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-004</t>
@@ -605,7 +642,7 @@
     <t xml:space="preserve">UAT User 1 has UAT Challenge A; UAT User 2 exists</t>
   </si>
   <si>
-    <t xml:space="preserve">User 2 email: uat.sdt.user2@example.com
+    <t xml:space="preserve">User 2 email: sdt.user2@example.com
 Password: dedicated UAT password</t>
   </si>
   <si>
@@ -736,6 +773,9 @@
     <t xml:space="preserve">Challenge cannot start, wrong details appear, or duplicate active challenge is created.</t>
   </si>
   <si>
+    <t xml:space="preserve">Challenge starts with correct rules and settings.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-017</t>
   </si>
   <si>
@@ -1000,6 +1040,9 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
+    <t xml:space="preserve">10 October 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Decision</t>
   </si>
   <si>
@@ -1007,6 +1050,9 @@
   </si>
   <si>
     <t xml:space="preserve">Approved By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Works as intended</t>
   </si>
   <si>
     <t xml:space="preserve">Acceptance statement: The tester confirms that SDT V2 has been validated against the approved V2 change requests and retained core functionality in the production environment. Any exceptions must be recorded in the Defect Log and referenced in this sign-off.</t>
@@ -1019,11 +1065,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1074,6 +1121,13 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1149,36 +1203,40 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1219,7 +1277,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE7E6E6"/>
+          <fgColor rgb="FFE2F0D9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1227,7 +1285,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF595959"/>
+          <fgColor rgb="FF375623"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1423,8 +1481,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterUATCases" displayName="MasterUATCases" ref="A4:N29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterUATCases" displayName="MasterUATCases" ref="A4:M29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="13">
     <tableColumn id="1" name="Test Case ID"/>
     <tableColumn id="2" name="CR / Area"/>
     <tableColumn id="3" name="Priority"/>
@@ -1436,9 +1494,8 @@
     <tableColumn id="9" name="Alternative / Failure Result"/>
     <tableColumn id="10" name="Actual Result"/>
     <tableColumn id="11" name="Status"/>
-    <tableColumn id="12" name="Evidence Ref"/>
-    <tableColumn id="13" name="Defect ID"/>
-    <tableColumn id="14" name="Comments"/>
+    <tableColumn id="12" name="Defect ID"/>
+    <tableColumn id="13" name="Comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1641,486 +1698,494 @@
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <f aca="false">COUNTA('UAT Test Cases'!A5:A29)</f>
         <v>25</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="3" t="n">
+      <c r="A24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="4" t="n">
         <f aca="false">COUNTIF('UAT Test Cases'!K5:K29,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="3" t="n">
+      <c r="A25" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="4" t="n">
         <f aca="false">COUNTIF('UAT Test Cases'!K5:K29,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="3" t="n">
+      <c r="A26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="4" t="n">
         <f aca="false">COUNTIF('UAT Test Cases'!K5:K29,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <f aca="false">COUNTIF('UAT Test Cases'!K5:K29,"Not Run")</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="3" t="n">
-        <f aca="false">COUNTIF('UAT Test Cases'!K5:K29,"Not Run")</f>
-        <v>25</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2143,1008 +2208,1131 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="L6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="F29" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K29">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
@@ -3170,6 +3358,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1" display="https://self-development-tracker-sdt.vercel.app/"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3178,7 +3369,7 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3191,570 +3382,570 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="35"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>285</v>
+      <c r="L3" s="5" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3795,103 +3986,113 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="3"/>
+      <c r="E4" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F5" s="3"/>
+      <c r="A5" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="B6" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/v2/04_SDT_V2_Production_UAT_Pack.xlsx
+++ b/docs/v2/04_SDT_V2_Production_UAT_Pack.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UAT Summary" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="301">
   <si>
     <t xml:space="preserve">SDT V2 - Production User Acceptance Testing (UAT) Pack</t>
   </si>
@@ -312,35 +312,8 @@
     <t xml:space="preserve">Blank page, 404/500 error, configuration error, or application fails to render.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">App/website loads properly @ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://self-development-tracker-sdt.vercel.app/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.
+    <t xml:space="preserve">App/website loads properly @ https://self-development-tracker-sdt.vercel.app/.
 Authentication screen correctly appears.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Pass</t>
@@ -390,7 +363,7 @@
     <t xml:space="preserve">Login page is open</t>
   </si>
   <si>
-    <t xml:space="preserve">Email: uat.sdt.user1@example.com
+    <t xml:space="preserve">Email: sdt.user1@example.com
 Password: deliberately incorrect password</t>
   </si>
   <si>
@@ -1007,6 +980,9 @@
     <t xml:space="preserve">SDT V2 - UAT Defect Log</t>
   </si>
   <si>
+    <t xml:space="preserve">No defects identified during Production UAT </t>
+  </si>
+  <si>
     <t xml:space="preserve">Related Test Case</t>
   </si>
   <si>
@@ -1025,9 +1001,6 @@
     <t xml:space="preserve">Resolution / Retest Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Open</t>
-  </si>
-  <si>
     <t xml:space="preserve">SDT V2 - Production UAT Sign-Off</t>
   </si>
   <si>
@@ -1040,7 +1013,7 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">10 October 2026</t>
+    <t xml:space="preserve">3 October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Decision</t>
@@ -1203,7 +1176,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1237,6 +1210,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1501,26 +1482,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="UATDefects" displayName="UATDefects" ref="A3:L28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="12">
-    <tableColumn id="1" name="Defect ID"/>
-    <tableColumn id="2" name="Related Test Case"/>
-    <tableColumn id="3" name="Date Raised"/>
-    <tableColumn id="4" name="Summary"/>
-    <tableColumn id="5" name="Steps / Context"/>
-    <tableColumn id="6" name="Expected Result"/>
-    <tableColumn id="7" name="Actual Result"/>
-    <tableColumn id="8" name="Severity"/>
-    <tableColumn id="9" name="Priority"/>
-    <tableColumn id="10" name="Status"/>
-    <tableColumn id="11" name="Owner"/>
-    <tableColumn id="12" name="Resolution / Retest Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
   <a:themeElements>
@@ -2223,7 +2184,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2329,7 +2290,7 @@
       <c r="I5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="9" t="s">
         <v>95</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -3359,7 +3320,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" display="https://self-development-tracker-sdt.vercel.app/"/>
+    <hyperlink ref="J5" r:id="rId1" display="App/website loads properly @ https://self-development-tracker-sdt.vercel.app/.&#10;Authentication screen correctly appears."/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3379,10 +3340,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
@@ -3409,21 +3370,26 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
+    <row r="2" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>83</v>
@@ -3432,7 +3398,7 @@
         <v>85</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>26</v>
@@ -3444,527 +3410,38 @@
         <v>29</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-    </row>
+    </row>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H28" type="list">
-      <formula1>"Critical,High,Medium,Low"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I4:I28" type="list">
-      <formula1>"Critical,High,Medium,Low"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J4:J28" type="list">
-      <formula1>"Open,In Progress,Ready for Retest,Closed,Deferred"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3972,9 +3449,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <tableParts/>
 </worksheet>
 </file>
 
